--- a/excel_project/部门考勤数据/人力行政部 (HR&ADM)_异常考勤数据.xlsx
+++ b/excel_project/部门考勤数据/人力行政部 (HR&ADM)_异常考勤数据.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>陈嘉怡</t>
+          <t>陈嘉怡-Alicia Chan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
